--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.25680263448292</v>
+        <v>3.941730428103475</v>
       </c>
       <c r="D2" t="n">
-        <v>23.73263110907214</v>
+        <v>3.856552555224224</v>
       </c>
       <c r="E2" t="n">
-        <v>5.519031900496109</v>
+        <v>0.8968426838306178</v>
       </c>
       <c r="F2" t="n">
-        <v>8.432237316369168</v>
+        <v>1.37023856390999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.16350609402456</v>
+        <v>5.226569740278991</v>
       </c>
       <c r="D3" t="n">
-        <v>38.40841826938755</v>
+        <v>6.241367968775478</v>
       </c>
       <c r="E3" t="n">
-        <v>5.519031900496109</v>
+        <v>0.8968426838306178</v>
       </c>
       <c r="F3" t="n">
-        <v>8.432237316369168</v>
+        <v>1.37023856390999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.71374771035165</v>
+        <v>3.040984002932143</v>
       </c>
       <c r="D4" t="n">
-        <v>18.48371527870407</v>
+        <v>3.003603732789412</v>
       </c>
       <c r="E4" t="n">
-        <v>5.519031900496109</v>
+        <v>0.8968426838306178</v>
       </c>
       <c r="F4" t="n">
-        <v>8.432237316369168</v>
+        <v>1.37023856390999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
